--- a/data/raw/inventory/Week 27/Nexlev/Inventory Snapshot.xlsx
+++ b/data/raw/inventory/Week 27/Nexlev/Inventory Snapshot.xlsx
@@ -1286,7 +1286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L259"/>
+  <dimension ref="A1:L260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="12.88671875" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -9180,6 +9180,36 @@
         </is>
       </c>
       <c r="K259" s="8" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>FBK79271</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>B0DQ8W1RBV</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>V-01 RG</t>
+        </is>
+      </c>
+      <c r="I260" t="n">
+        <v>53</v>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>AMPM</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L259"/>
